--- a/PESCO2SynergiMdb/DataMapping4Mdb.xlsx
+++ b/PESCO2SynergiMdb/DataMapping4Mdb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Barqaab\PESCO2SynergiMdb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2895516E-848C-473A-B7EA-03EB3AE593D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A82E03-00AB-4BF0-BD31-377A8F561203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="728" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="728" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FieldDataNInstsection" sheetId="15" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6254" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6279" uniqueCount="263">
   <si>
     <t>ID</t>
   </si>
@@ -797,6 +797,43 @@
   <si>
     <t>T-17280920360</t>
   </si>
+  <si>
+    <t>s= from
+e= to</t>
+  </si>
+  <si>
+    <t>only pick with E rows</t>
+  </si>
+  <si>
+    <t>con_size_n</t>
+  </si>
+  <si>
+    <t>121.9 to all rows</t>
+  </si>
+  <si>
+    <t>91.4 to all rows</t>
+  </si>
+  <si>
+    <t>cumulative sum of x, y, from node to node</t>
+  </si>
+  <si>
+    <t>SectionPhases
+if ryb =0
+if rybn =1</t>
+  </si>
+  <si>
+    <t>con_size_a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con_Size_B
+</t>
+  </si>
+  <si>
+    <t>Con_Size_c</t>
+  </si>
+  <si>
+    <t>blank</t>
+  </si>
 </sst>
 </file>
 
@@ -866,7 +903,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -874,6 +911,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1209,7 +1252,7 @@
     <col min="3" max="3" width="13.36328125" customWidth="1"/>
     <col min="4" max="4" width="17.54296875" customWidth="1"/>
     <col min="5" max="5" width="19.54296875" customWidth="1"/>
-    <col min="6" max="6" width="16.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
     <col min="7" max="7" width="20.453125" customWidth="1"/>
     <col min="8" max="8" width="16.90625" customWidth="1"/>
     <col min="9" max="9" width="23.08984375" customWidth="1"/>
@@ -1221,10 +1264,11 @@
     <col min="15" max="15" width="31.6328125" customWidth="1"/>
     <col min="16" max="16" width="29.08984375" customWidth="1"/>
     <col min="17" max="17" width="19.90625" customWidth="1"/>
-    <col min="18" max="18" width="20.81640625" customWidth="1"/>
+    <col min="18" max="18" width="24.81640625" customWidth="1"/>
     <col min="19" max="19" width="18.90625" customWidth="1"/>
-    <col min="20" max="20" width="15.7265625" customWidth="1"/>
+    <col min="20" max="20" width="27.08984375" customWidth="1"/>
     <col min="21" max="21" width="22.453125" customWidth="1"/>
+    <col min="22" max="22" width="25" customWidth="1"/>
     <col min="23" max="23" width="21" customWidth="1"/>
     <col min="24" max="24" width="19.453125" customWidth="1"/>
     <col min="25" max="25" width="17.54296875" customWidth="1"/>
@@ -1237,13 +1281,16 @@
     <col min="32" max="32" width="18.7265625" customWidth="1"/>
     <col min="33" max="33" width="16.08984375" customWidth="1"/>
     <col min="34" max="34" width="24.08984375" customWidth="1"/>
-    <col min="35" max="35" width="22.6328125" customWidth="1"/>
+    <col min="35" max="35" width="31.1796875" customWidth="1"/>
     <col min="36" max="36" width="21.36328125" customWidth="1"/>
     <col min="37" max="37" width="24.36328125" customWidth="1"/>
     <col min="38" max="38" width="20.36328125" customWidth="1"/>
     <col min="39" max="39" width="21.36328125" customWidth="1"/>
     <col min="40" max="40" width="21.54296875" customWidth="1"/>
     <col min="41" max="41" width="26.08984375" customWidth="1"/>
+    <col min="42" max="42" width="16.08984375" customWidth="1"/>
+    <col min="43" max="43" width="12.54296875" customWidth="1"/>
+    <col min="44" max="44" width="17.6328125" customWidth="1"/>
     <col min="45" max="45" width="28.90625" customWidth="1"/>
     <col min="46" max="46" width="28.453125" customWidth="1"/>
     <col min="47" max="47" width="17.7265625" customWidth="1"/>
@@ -5249,12 +5296,183 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:60" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="27" spans="1:60" x14ac:dyDescent="0.35">
+      <c r="D25" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F25" t="s">
+        <v>253</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="I25" t="s">
+        <v>254</v>
+      </c>
+      <c r="T25" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="W25" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="X25" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="26" spans="1:60" ht="29" x14ac:dyDescent="0.35">
+      <c r="H26" s="7"/>
+      <c r="J26" t="s">
+        <v>255</v>
+      </c>
+      <c r="K26" t="s">
+        <v>256</v>
+      </c>
+      <c r="L26">
+        <v>9.1</v>
+      </c>
+      <c r="M26">
+        <v>40</v>
+      </c>
+      <c r="N26">
+        <v>10</v>
+      </c>
+      <c r="O26">
+        <v>40</v>
+      </c>
+      <c r="P26">
+        <v>30</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="R26">
+        <v>2</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>100</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>262</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>262</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>143</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>143</v>
+      </c>
+      <c r="AO26">
+        <v>100</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>262</v>
+      </c>
+      <c r="AQ26" t="s">
+        <v>262</v>
+      </c>
+      <c r="AR26">
+        <v>1</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>100</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>1</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="s">
+        <v>262</v>
+      </c>
+      <c r="BB26" t="s">
+        <v>144</v>
+      </c>
+      <c r="BC26" t="s">
+        <v>262</v>
+      </c>
+      <c r="BD26" t="s">
+        <v>262</v>
+      </c>
+      <c r="BE26">
+        <v>1</v>
+      </c>
+      <c r="BF26">
+        <v>1</v>
+      </c>
+      <c r="BG26">
+        <v>1</v>
+      </c>
+      <c r="BH26" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>148</v>
       </c>
@@ -5271,16 +5489,16 @@
         <v>147</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>147</v>
+      <c r="H27" s="8" t="s">
+        <v>259</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>147</v>
@@ -5321,11 +5539,11 @@
       <c r="V27" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="W27" s="4" t="s">
-        <v>147</v>
+      <c r="W27" s="8" t="s">
+        <v>260</v>
       </c>
       <c r="X27" s="4" t="s">
-        <v>147</v>
+        <v>261</v>
       </c>
       <c r="Y27" s="4" t="s">
         <v>147</v>
